--- a/excel-files/MANDALUYONG/HIGHWAY HILLS INTEGRATED SCHOOL.xlsx
+++ b/excel-files/MANDALUYONG/HIGHWAY HILLS INTEGRATED SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29728"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="343" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C0F2188-97AC-4F8C-96FE-5CB49DD67DF7}"/>
+  <xr:revisionPtr revIDLastSave="402" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FD1C7EE-DE54-47E7-B7A2-25065A8AD94B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="95">
   <si>
     <t>Grade Level</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>Reading and Literacy</t>
+  </si>
+  <si>
+    <t>CO</t>
   </si>
   <si>
     <t>Language</t>
@@ -98,9 +101,6 @@
   </si>
   <si>
     <t>Music and Arts</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>VE</t>
@@ -3549,16 +3549,22 @@
         <v>8</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="5"/>
+      <c r="D2" s="1">
+        <v>415</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G2" s="3">
         <f>IF((C2-D2)&lt;0,0,C2-D2)</f>
         <v>0</v>
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>0</v>
+        <v>415</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="29.25" customHeight="1">
@@ -3566,19 +3572,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1">
+        <v>415</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="5"/>
       <c r="G3" s="3">
         <f>IF((C3-D3)&lt;0,0,C3-D3)</f>
         <v>0</v>
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>0</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" customHeight="1">
@@ -3586,19 +3598,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="5"/>
+      <c r="D4" s="1">
+        <v>415</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G4" s="3">
         <f>IF((C4-D4)&lt;0,0,C4-D4)</f>
         <v>0</v>
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>0</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25.5" customHeight="1">
@@ -3606,27 +3624,33 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
+      <c r="D5" s="1">
+        <v>415</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
         <v>0</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.149999999999999">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="46.5" customHeight="1">
       <c r="A6" s="1">
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -3671,7 +3695,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -3691,7 +3715,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -3711,7 +3735,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -3731,7 +3755,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -3776,7 +3800,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -3796,7 +3820,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -3816,7 +3840,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3836,7 +3860,7 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -3856,7 +3880,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -3886,19 +3910,25 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="5"/>
+      <c r="D21" s="1">
+        <v>458</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G21" s="3">
         <f t="shared" ref="G21:G29" si="4">IF((C21-D21)&lt;0,0,C21-D21)</f>
         <v>0</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
-        <v>0</v>
+        <v>458</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24" customHeight="1">
@@ -3906,39 +3936,51 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="5"/>
+      <c r="D22" s="1">
+        <v>458</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="19.149999999999999">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="19.5">
       <c r="A23" s="1">
         <v>4</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="5"/>
+      <c r="D23" s="1">
+        <v>458</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="27" customHeight="1">
@@ -3946,19 +3988,25 @@
         <v>4</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="5"/>
+      <c r="D24" s="1">
+        <v>458</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>458</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="33.75" customHeight="1">
@@ -3966,7 +4014,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -3986,7 +4034,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -4006,7 +4054,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -4026,7 +4074,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -4046,19 +4094,25 @@
         <v>4</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="D29" s="1">
+        <v>440</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4076,19 +4130,25 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+      <c r="D31" s="1">
+        <v>402</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>402</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4096,7 +4156,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -4116,7 +4176,7 @@
         <v>5</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -4136,7 +4196,7 @@
         <v>5</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -4156,19 +4216,25 @@
         <v>5</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="5"/>
+      <c r="D35" s="1">
+        <v>362</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="27.75" customHeight="1">
@@ -4176,19 +4242,25 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
+      <c r="D36" s="1">
+        <v>402</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>402</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4196,19 +4268,25 @@
         <v>5</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+      <c r="D37" s="1">
+        <v>406</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>406</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4216,19 +4294,25 @@
         <v>5</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="D38" s="1">
+        <v>402</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4236,7 +4320,7 @@
         <v>5</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -4266,7 +4350,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -4286,7 +4370,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -4306,7 +4390,7 @@
         <v>6</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -4326,7 +4410,7 @@
         <v>6</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -4346,7 +4430,7 @@
         <v>6</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -4366,7 +4450,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4386,7 +4470,7 @@
         <v>6</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -4406,7 +4490,7 @@
         <v>6</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -4426,7 +4510,7 @@
         <v>6</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -4456,7 +4540,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C51" s="10">
         <v>314</v>
@@ -4468,7 +4552,7 @@
         <v>2025</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G51" s="3">
         <f t="shared" ref="G51:G59" si="10">IF((C51-D51)&lt;0,0,C51-D51)</f>
@@ -4484,23 +4568,27 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C52" s="10">
         <v>314</v>
       </c>
       <c r="D52" s="10">
-        <v>0</v>
-      </c>
-      <c r="E52" s="10"/>
-      <c r="F52" s="12"/>
+        <v>617</v>
+      </c>
+      <c r="E52" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="G52" s="3">
         <f t="shared" si="10"/>
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="H52" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>303</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="27.75" customHeight="1">
@@ -4508,7 +4596,7 @@
         <v>7</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C53" s="10">
         <v>314</v>
@@ -4520,7 +4608,7 @@
         <v>2024</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G53" s="3">
         <f t="shared" si="10"/>
@@ -4542,17 +4630,21 @@
         <v>314</v>
       </c>
       <c r="D54" s="10">
-        <v>0</v>
-      </c>
-      <c r="E54" s="10"/>
-      <c r="F54" s="12"/>
+        <v>617</v>
+      </c>
+      <c r="E54" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="G54" s="3">
         <f t="shared" si="10"/>
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="H54" s="4">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>303</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="39" customHeight="1">
@@ -4560,7 +4652,7 @@
         <v>7</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C55" s="10">
         <v>314</v>
@@ -4572,7 +4664,7 @@
         <v>2025</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G55" s="3">
         <f t="shared" si="10"/>
@@ -4588,7 +4680,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C56" s="10">
         <v>314</v>
@@ -4600,7 +4692,7 @@
         <v>2024</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G56" s="3">
         <f t="shared" si="10"/>
@@ -4616,7 +4708,7 @@
         <v>7</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C57" s="10">
         <v>314</v>
@@ -4628,7 +4720,7 @@
         <v>2025</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G57" s="3">
         <f t="shared" si="10"/>
@@ -4656,7 +4748,7 @@
         <v>2025</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G58" s="3">
         <f t="shared" si="10"/>
@@ -4672,7 +4764,7 @@
         <v>7</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C59" s="10">
         <v>314</v>
@@ -4684,7 +4776,7 @@
         <v>2025</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G59" s="3">
         <f t="shared" si="10"/>
@@ -4710,7 +4802,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C61" s="10">
         <v>335</v>
@@ -4734,7 +4826,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C62" s="10">
         <v>335</v>
@@ -4758,7 +4850,7 @@
         <v>8</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C63" s="10">
         <v>335</v>
@@ -4770,7 +4862,7 @@
         <v>2025</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G63" s="3">
         <f t="shared" si="12"/>
@@ -4798,7 +4890,7 @@
         <v>2025</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G64" s="3">
         <f t="shared" si="12"/>
@@ -4838,23 +4930,27 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C66" s="10">
         <v>335</v>
       </c>
       <c r="D66" s="10">
-        <v>0</v>
-      </c>
-      <c r="E66" s="10"/>
-      <c r="F66" s="12"/>
+        <v>488</v>
+      </c>
+      <c r="E66" s="10">
+        <v>2026</v>
+      </c>
+      <c r="F66" s="12" t="s">
+        <v>9</v>
+      </c>
       <c r="G66" s="3">
         <f t="shared" si="12"/>
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="H66" s="4">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>153</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="27.75" customHeight="1">
@@ -4862,7 +4958,7 @@
         <v>8</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C67" s="10">
         <v>335</v>
@@ -4910,7 +5006,7 @@
         <v>8</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C69" s="10">
         <v>335</v>
@@ -4944,7 +5040,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C71" s="10">
         <v>339</v>
@@ -4968,7 +5064,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C72" s="10">
         <v>339</v>
@@ -4980,7 +5076,7 @@
         <v>2024</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G72" s="3">
         <f t="shared" si="14"/>
@@ -4996,7 +5092,7 @@
         <v>9</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C73" s="10">
         <v>339</v>
@@ -5068,7 +5164,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C76" s="10">
         <v>339</v>
@@ -5092,7 +5188,7 @@
         <v>9</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C77" s="10">
         <v>339</v>
@@ -5140,7 +5236,7 @@
         <v>9</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C79" s="10">
         <v>339</v>
@@ -5174,7 +5270,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C81" s="10">
         <v>426</v>
@@ -5198,7 +5294,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C82" s="10">
         <v>426</v>
@@ -5210,7 +5306,7 @@
         <v>2024</v>
       </c>
       <c r="F82" s="12" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G82" s="3">
         <f t="shared" si="16"/>
@@ -5226,7 +5322,7 @@
         <v>10</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C83" s="10">
         <v>426</v>
@@ -5298,7 +5394,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C86" s="10">
         <v>426</v>
@@ -5322,7 +5418,7 @@
         <v>10</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C87" s="10">
         <v>426</v>
@@ -5370,7 +5466,7 @@
         <v>10</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C89" s="10">
         <v>426</v>
@@ -5416,7 +5512,7 @@
         <v>2024</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G91" s="3">
         <f t="shared" ref="G91:G101" si="18">IF((C91-D91)&lt;0,0,C91-D91)</f>
@@ -5468,7 +5564,7 @@
         <v>2024</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G93" s="3">
         <f t="shared" si="18"/>
@@ -5496,7 +5592,7 @@
         <v>2025</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G94" s="3">
         <f t="shared" si="18"/>
@@ -5524,7 +5620,7 @@
         <v>2025</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G95" s="3">
         <f t="shared" si="18"/>
@@ -5552,7 +5648,7 @@
         <v>2025</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G96" s="3">
         <f t="shared" si="18"/>
@@ -5580,7 +5676,7 @@
         <v>2025</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G97" s="3">
         <f t="shared" si="18"/>
@@ -5608,7 +5704,7 @@
         <v>2025</v>
       </c>
       <c r="F98" s="31" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G98" s="42">
         <f t="shared" si="18"/>
@@ -5636,7 +5732,7 @@
         <v>2025</v>
       </c>
       <c r="F99" s="31" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G99" s="42">
         <f t="shared" si="18"/>
@@ -5664,7 +5760,7 @@
         <v>2025</v>
       </c>
       <c r="F100" s="31" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G100" s="42">
         <f t="shared" ref="G100" si="20">IF((C100-D100)&lt;0,0,C100-D100)</f>
@@ -5692,7 +5788,7 @@
         <v>2024</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G101" s="42">
         <f t="shared" si="18"/>
@@ -5710,10 +5806,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E101" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E101 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E2:E6 E14:E19 E8:E12 E21:E29" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F101" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F2:F6 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F91:F101 F8:F12 F21:F29" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5730,7 +5826,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -6016,7 +6112,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="5">
@@ -6085,7 +6181,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5">
@@ -6154,7 +6250,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -6223,7 +6319,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -6292,7 +6388,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -6361,7 +6457,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6581,7 +6677,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5">
@@ -6650,7 +6746,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="5">
@@ -6719,7 +6815,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -6788,7 +6884,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -6857,7 +6953,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="5">
@@ -6926,7 +7022,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="5">
@@ -7147,7 +7243,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -7216,7 +7312,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="5">
@@ -7285,7 +7381,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -7354,7 +7450,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -7423,7 +7519,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -7492,7 +7588,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -7561,7 +7657,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="5">
@@ -7713,7 +7809,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7782,7 +7878,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7851,7 +7947,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="5">
@@ -7920,7 +8016,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -7989,7 +8085,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="5">
@@ -8058,7 +8154,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -8127,7 +8223,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="5">
@@ -8196,7 +8292,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="5">
@@ -8265,7 +8361,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="5">
@@ -8348,7 +8444,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -8417,7 +8513,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -8486,7 +8582,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="5">
@@ -8555,7 +8651,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="5">
@@ -8624,7 +8720,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="5">
@@ -8693,7 +8789,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -8762,7 +8858,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="5">
@@ -8831,7 +8927,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="5">
@@ -8900,7 +8996,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="5">
@@ -8983,7 +9079,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -9052,7 +9148,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -9121,7 +9217,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -9190,7 +9286,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -9259,7 +9355,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="5">
@@ -9328,7 +9424,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9397,7 +9493,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="5">
@@ -9466,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -9535,7 +9631,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="5">
@@ -9618,7 +9714,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9687,7 +9783,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9756,7 +9852,7 @@
         <v>7</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="12">
@@ -9894,7 +9990,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -9963,7 +10059,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -10032,7 +10128,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -10170,7 +10266,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -10253,7 +10349,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10322,7 +10418,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10391,7 +10487,7 @@
         <v>8</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="12">
@@ -10598,7 +10694,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10667,7 +10763,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -10805,7 +10901,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -10888,7 +10984,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10957,7 +11053,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -11026,7 +11122,7 @@
         <v>9</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="12">
@@ -11233,7 +11329,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -11302,7 +11398,7 @@
         <v>9</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -11440,7 +11536,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -11523,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11592,7 +11688,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11661,7 +11757,7 @@
         <v>10</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="12">
@@ -11868,7 +11964,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -11937,7 +12033,7 @@
         <v>10</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="12">
@@ -12075,7 +12171,7 @@
         <v>10</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -13703,186 +13799,6 @@
       <c r="AA127" s="5">
         <f t="shared" si="21"/>
         <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
@@ -13902,8 +13818,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13925,7 +13841,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14133,7 +14049,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="5">
@@ -14202,7 +14118,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="5">
@@ -14271,7 +14187,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="5">
@@ -14340,7 +14256,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5">
@@ -14409,7 +14325,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14478,7 +14394,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14686,7 +14602,7 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="5">
@@ -14755,7 +14671,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="5">
@@ -14828,7 +14744,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="5">
@@ -14905,7 +14821,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="5">
@@ -14978,7 +14894,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -15055,7 +14971,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -15267,7 +15183,7 @@
         <v>3</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="5">
@@ -15336,7 +15252,7 @@
         <v>3</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="5">
@@ -15409,7 +15325,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15482,7 +15398,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="5">
@@ -15555,7 +15471,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -15628,7 +15544,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -15701,7 +15617,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -15844,7 +15760,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15913,7 +15829,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -15982,7 +15898,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -16051,7 +15967,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -16120,7 +16036,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="5">
@@ -16189,7 +16105,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -16396,7 +16312,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="5">
@@ -16604,7 +16520,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16677,7 +16593,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16752,7 +16668,7 @@
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="5">
@@ -16825,7 +16741,7 @@
         <v>5</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="5">
@@ -16898,7 +16814,7 @@
         <v>5</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="5">
@@ -16971,7 +16887,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -17186,7 +17102,7 @@
         <v>5</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="5">
@@ -17402,7 +17318,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -17481,7 +17397,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -17560,7 +17476,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="5">
@@ -17643,7 +17559,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -17712,7 +17628,7 @@
         <v>6</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="5">
@@ -17789,7 +17705,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -18020,7 +17936,7 @@
         <v>6</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="5">
@@ -18246,7 +18162,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -18315,7 +18231,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -18384,7 +18300,7 @@
         <v>7</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="12">
@@ -18522,7 +18438,7 @@
         <v>7</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="12">
@@ -18591,7 +18507,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -19006,7 +18922,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -19075,7 +18991,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -19144,7 +19060,7 @@
         <v>8</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="12">
@@ -19351,7 +19267,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -19766,7 +19682,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C91" s="10">
         <v>339</v>
@@ -19843,7 +19759,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C92" s="10">
         <v>339</v>
@@ -19932,7 +19848,7 @@
         <v>9</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C93" s="10">
         <v>339</v>
@@ -20181,7 +20097,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C96" s="10">
         <v>339</v>
@@ -20650,7 +20566,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C103" s="10">
         <v>426</v>
@@ -20745,7 +20661,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C104" s="10">
         <v>426</v>
@@ -20834,7 +20750,7 @@
         <v>10</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C105" s="10">
         <v>426</v>
@@ -21095,7 +21011,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C108" s="10">
         <v>426</v>
@@ -22640,186 +22556,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22837,8 +22573,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 G91:G101 S91:S101 Y103:Y113 M103:M113 M115:M122 S103:S113 M91:M101 Y91:Y101 G103:G113" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 F103:F113 L103:L113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 X103:X113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 X91:X101 R91:R101 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 R103:R113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
